--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלוש ציפורים דמיון חופשי</v>
+        <v>שלוש ציפורים – דמיון חופשי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-01</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלוש ציפורים דמיון חופשי</v>
+        <v>שלוש ציפורים – דמיון חופשי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלוש ציפורים – דמיון חופשי</v>
+        <v>יוסף עבאדי - רגעים של אושר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%a9-%d7%a6%d7%99%d7%a4%d7%95%d7%a8%d7%99%d7%9d-%d7%93%d7%9e%d7%99%d7%95%d7%9f-%d7%97%d7%95%d7%a4%d7%a9%d7%99/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409439&amp;sid=755baf5a9e427242a5603345f7826207</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-01</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"דמיון חופשי” של יצחק קלפטר הוא מן השירים שבהם הפשטות הלירית נושאת על גבה עומק רגשי גדול. זהו שיר על אהבה שאינה מתממשת, על פער בין תשוקה למציאות, ועל המקום שבו הדמיון הופך למרחב מפלט – אך גם למרחב של</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,316 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלוש ציפורים – דמיון חופשי</v>
+        <v>יוסף עבאדי - רגעים של אושר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>יהונתן ישראל - אבא תודה</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409438&amp;sid=755baf5a9e427242a5603345f7826207</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>יהונתן ישראל - אבא תודה</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>דניאל יטיב - תודה</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409437&amp;sid=755baf5a9e427242a5603345f7826207</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>דניאל יטיב - תודה</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>בניה ברבי - מהודו להודו</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409436&amp;sid=755baf5a9e427242a5603345f7826207</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>בניה ברבי - מהודו להודו</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>בניה ברבי - מהודו להודו</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409435&amp;sid=755baf5a9e427242a5603345f7826207</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>בניה ברבי - מהודו להודו</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>בן שוקרון - יותר שמיים</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409434&amp;sid=755baf5a9e427242a5603345f7826207</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>בן שוקרון - יותר שמיים</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אסף בר נתן - אם זה שורף</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409433&amp;sid=755baf5a9e427242a5603345f7826207</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אסף בר נתן - אם זה שורף</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>איציק וינגרטן - רק מנגינות</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409432&amp;sid=755baf5a9e427242a5603345f7826207</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>איציק וינגרטן - רק מנגינות</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אביחי פרץ - מי לי</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409431&amp;sid=755baf5a9e427242a5603345f7826207</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אביחי פרץ - מי לי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יוסף עבאדי - רגעים של אושר</v>
+        <v>פרחי ירושלים - שיר היובל 50 שנה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409439&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409444&amp;sid=c5c30978038848a81687864b9fc464f8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-01</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יוסף עבאדי - רגעים של אושר</v>
+        <v>פרחי ירושלים - שיר היובל 50 שנה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יהונתן ישראל - אבא תודה</v>
+        <v>פרחי ירושלים - סומלילנד</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409438&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409443&amp;sid=c5c30978038848a81687864b9fc464f8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-01</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יהונתן ישראל - אבא תודה</v>
+        <v>פרחי ירושלים - סומלילנד</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>דניאל יטיב - תודה</v>
+        <v>מתנאל סבח - שדרות דוממת</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409437&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409442&amp;sid=c5c30978038848a81687864b9fc464f8</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-01</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>דניאל יטיב - תודה</v>
+        <v>מתנאל סבח - שדרות דוממת</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>בניה ברבי - מהודו להודו</v>
+        <v>מני חן &amp; שום ראפר - שימי לב, מה ייתן לך</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409436&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409441&amp;sid=c5c30978038848a81687864b9fc464f8</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-01</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>בניה ברבי - מהודו להודו</v>
+        <v>מני חן &amp; שום ראפר - שימי לב, מה ייתן לך</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>בניה ברבי - מהודו להודו</v>
+        <v>אורי זר - חוזר לילדות</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409435&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409440&amp;sid=c5c30978038848a81687864b9fc464f8</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-01</v>
@@ -621,164 +621,12 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>בניה ברבי - מהודו להודו</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>בן שוקרון - יותר שמיים</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409434&amp;sid=755baf5a9e427242a5603345f7826207</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>בן שוקרון - יותר שמיים</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אסף בר נתן - אם זה שורף</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409433&amp;sid=755baf5a9e427242a5603345f7826207</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אסף בר נתן - אם זה שורף</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>איציק וינגרטן - רק מנגינות</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409432&amp;sid=755baf5a9e427242a5603345f7826207</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>איציק וינגרטן - רק מנגינות</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אביחי פרץ - מי לי</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409431&amp;sid=755baf5a9e427242a5603345f7826207</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אביחי פרץ - מי לי</v>
+        <v>אורי זר - חוזר לילדות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פרחי ירושלים - שיר היובל 50 שנה</v>
+        <v>ששון שאולוב - חשבונות שמיים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409444&amp;sid=c5c30978038848a81687864b9fc464f8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409446&amp;sid=27f51e4d97173c14aa9eadc22e457f7c</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-01</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פרחי ירושלים - שיר היובל 50 שנה</v>
+        <v>ששון שאולוב - חשבונות שמיים</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>פרחי ירושלים - סומלילנד</v>
+        <v>רפאל שילוני - מחכה לך</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409443&amp;sid=c5c30978038848a81687864b9fc464f8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409445&amp;sid=27f51e4d97173c14aa9eadc22e457f7c</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-01</v>
@@ -507,126 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>פרחי ירושלים - סומלילנד</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>מתנאל סבח - שדרות דוממת</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409442&amp;sid=c5c30978038848a81687864b9fc464f8</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>מתנאל סבח - שדרות דוממת</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>מני חן &amp; שום ראפר - שימי לב, מה ייתן לך</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409441&amp;sid=c5c30978038848a81687864b9fc464f8</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>מני חן &amp; שום ראפר - שימי לב, מה ייתן לך</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>אורי זר - חוזר לילדות</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409440&amp;sid=c5c30978038848a81687864b9fc464f8</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>אורי זר - חוזר לילדות</v>
+        <v>רפאל שילוני - מחכה לך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ששון שאולוב - חשבונות שמיים</v>
+        <v>בן שוקרון – יותר שמיים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409446&amp;sid=27f51e4d97173c14aa9eadc22e457f7c</v>
+        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%a9%d7%95%d7%a7%d7%a8%d7%95%d7%9f-%d7%99%d7%95%d7%aa%d7%a8-%d7%a9%d7%9e%d7%99%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>“יותר שמיים” של בן שוקרון הוא שיר אבל אישי שנשען על מציאות קשה, אך בוחר לבטא אותה דרך עדינות, שבריריות ואמונה, שירה מדוכדכת נרגשת ולא דרך זעם או פאתוס. הידיעה שהשיר נכתב בעקבות אובדן חבר קרוב במהלך אירוע צבאי בעזה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ששון שאולוב - חשבונות שמיים</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>רפאל שילוני - מחכה לך</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409445&amp;sid=27f51e4d97173c14aa9eadc22e457f7c</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>רפאל שילוני - מחכה לך</v>
+        <v>בן שוקרון – יותר שמיים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בן שוקרון – יותר שמיים</v>
+        <v>טונה – הייתי שם</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-02</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%a9%d7%95%d7%a7%d7%a8%d7%95%d7%9f-%d7%99%d7%95%d7%aa%d7%a8-%d7%a9%d7%9e%d7%99%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%a0%d7%94-%d7%94%d7%99%d7%99%d7%aa%d7%99-%d7%a9%d7%9d/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-02</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“יותר שמיים” של בן שוקרון הוא שיר אבל אישי שנשען על מציאות קשה, אך בוחר לבטא אותה דרך עדינות, שבריריות ואמונה, שירה מדוכדכת נרגשת ולא דרך זעם או פאתוס. הידיעה שהשיר נכתב בעקבות אובדן חבר קרוב במהלך אירוע צבאי בעזה</v>
+        <v>טונה מריץ ראפ אוטוביוגרפי שמבוסס על נרטיב של מאבק, התמדה וזהות. הוא משלב בין וידוי אישי לבין מסר אוניברסלי של הישרדות וצמיחה.הוא מציג את עצמו כ־ילד פריפריה שחולם על אימפריה – דמות שמגיעה ממקום מוחלש, חסר ביטחון וחסר משאבים, אך</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בן שוקרון – יותר שמיים</v>
+        <v>טונה – הייתי שם</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>טונה – הייתי שם</v>
+        <v>בניה ברבי – מהודו להודו</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-02</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%a0%d7%94-%d7%94%d7%99%d7%99%d7%aa%d7%99-%d7%a9%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%91%d7%a0%d7%99%d7%94-%d7%91%d7%a8%d7%91%d7%99-%d7%9e%d7%94%d7%95%d7%93%d7%95-%d7%9c%d7%94%d7%95%d7%93%d7%95/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-02</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>טונה מריץ ראפ אוטוביוגרפי שמבוסס על נרטיב של מאבק, התמדה וזהות. הוא משלב בין וידוי אישי לבין מסר אוניברסלי של הישרדות וצמיחה.הוא מציג את עצמו כ־ילד פריפריה שחולם על אימפריה – דמות שמגיעה ממקום מוחלש, חסר ביטחון וחסר משאבים, אך</v>
+        <v>בניה ברבי שר שיר שמשתלב במסורת ישראלית מוכרת של שירי מסע – מסע גיאוגרפי, נפשי ורוחני – שבסופו מתגלה אמת פשוטה אך עוצמתית: מה שחיפשת רחוק, היה קרוב כל הזמן. כבר בבית הראשון מתוארת תבנית ישראלית כמעט קלאסית: תרמיל, מטוס,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>טונה – הייתי שם</v>
+        <v>בניה ברבי – מהודו להודו</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בניה ברבי – מהודו להודו</v>
+        <v>נתנאל צ'אקי - ירח מלא</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-02</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%a0%d7%99%d7%94-%d7%91%d7%a8%d7%91%d7%99-%d7%9e%d7%94%d7%95%d7%93%d7%95-%d7%9c%d7%94%d7%95%d7%93%d7%95/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409457&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-02</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>בניה ברבי שר שיר שמשתלב במסורת ישראלית מוכרת של שירי מסע – מסע גיאוגרפי, נפשי ורוחני – שבסופו מתגלה אמת פשוטה אך עוצמתית: מה שחיפשת רחוק, היה קרוב כל הזמן. כבר בבית הראשון מתוארת תבנית ישראלית כמעט קלאסית: תרמיל, מטוס,</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,392 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בניה ברבי – מהודו להודו</v>
+        <v>נתנאל צ'אקי - ירח מלא</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>נתנאל ואנונו - לחיות איתך על הקצה</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409456&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>נתנאל ואנונו - לחיות איתך על הקצה</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נוי אגסי - בכל דרך שנלך</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409455&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נוי אגסי - בכל דרך שנלך</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מלי יקותיאל - כל היום</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409454&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מלי יקותיאל - כל היום</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מאור יפרח - אל תאכזבי אותי</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409453&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מאור יפרח - אל תאכזבי אותי</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יפתח גרינברג - כוכב</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409452&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יפתח גרינברג - כוכב</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>יאנג בוטה - שוקי לעדן</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409451&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>יאנג בוטה - שוקי לעדן</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>הרון הרון מארח את מנור שבת ופרחחי ירושלים - Every Time הורדה</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409450&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>הרון הרון מארח את מנור שבת ופרחחי ירושלים - Every Time הורדה</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>דניאל בן שימול - פתאום</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409449&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>דניאל בן שימול - פתאום</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>דורון מזר - מוזר להיות לבד</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409448&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>דורון מזר - מוזר להיות לבד</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אורן עדן - חייל של אמא</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409447&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אורן עדן - חייל של אמא</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נתנאל צ'אקי - ירח מלא</v>
+        <v>שמעון בוסקילה - מעליות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-02</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409457&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409460&amp;sid=596eb7a14186c6371d4797ff4f464372</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-02</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נתנאל צ'אקי - ירח מלא</v>
+        <v>שמעון בוסקילה - מעליות</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתנאל ואנונו - לחיות איתך על הקצה</v>
+        <v>שיר אמלי - חיכיתי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-02</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409456&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409459&amp;sid=596eb7a14186c6371d4797ff4f464372</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-02</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתנאל ואנונו - לחיות איתך על הקצה</v>
+        <v>שיר אמלי - חיכיתי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נוי אגסי - בכל דרך שנלך</v>
+        <v>שון בלו - אני בלו</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-02</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409455&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409458&amp;sid=596eb7a14186c6371d4797ff4f464372</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-02</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נוי אגסי - בכל דרך שנלך</v>
+        <v>שון בלו - אני בלו</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מלי יקותיאל - כל היום</v>
+        <v>יסמין מועלם ומוש בן ארי – דרך</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-02</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409454&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+        <v>https://yosmusic.com/%d7%99%d7%a1%d7%9e%d7%99%d7%9f-%d7%9e%d7%95%d7%a2%d7%9c%d7%9d-%d7%95%d7%9e%d7%95%d7%a9-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%93%d7%a8%d7%9a/</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-02</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>השיר "דרך" של מוש בן ארי הוא אחד משירי המסע האינטימיים והחשופים ביותר ברפרטואר שלו – מסע שאינו רק גיאוגרפי, אלא בראש ובראשונה רגשי. על רקע הביצוע החי המשותף עם יסמין מועלם באמפי שוני, מקבל השיר שכבה נוספת של עומק,</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -583,278 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מלי יקותיאל - כל היום</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>מאור יפרח - אל תאכזבי אותי</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409453&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>מאור יפרח - אל תאכזבי אותי</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>יפתח גרינברג - כוכב</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409452&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>יפתח גרינברג - כוכב</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>יאנג בוטה - שוקי לעדן</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409451&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>יאנג בוטה - שוקי לעדן</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>הרון הרון מארח את מנור שבת ופרחחי ירושלים - Every Time הורדה</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409450&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>הרון הרון מארח את מנור שבת ופרחחי ירושלים - Every Time הורדה</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>דניאל בן שימול - פתאום</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409449&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>דניאל בן שימול - פתאום</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>דורון מזר - מוזר להיות לבד</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409448&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>דורון מזר - מוזר להיות לבד</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אורן עדן - חייל של אמא</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409447&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אורן עדן - חייל של אמא</v>
+        <v>יסמין מועלם ומוש בן ארי – דרך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון בוסקילה - מעליות</v>
+        <v>אניה בוקשטיין – רק עכשיו</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409460&amp;sid=596eb7a14186c6371d4797ff4f464372</v>
+        <v>https://yosmusic.com/%d7%90%d7%a0%d7%99%d7%94-%d7%91%d7%95%d7%a7%d7%a9%d7%98%d7%99%d7%99%d7%9f-%d7%a8%d7%a7-%d7%a2%d7%9b%d7%a9%d7%99%d7%95/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>אניה בוקשטיין שרה וידוי אישי עטוף בפופ קליט ומאיר, כזה שמצליח להיות גם קליל ומרקיד וגם חשוף ובוגר. המעבר המוזיקלי מסמבה שקטה ואקוסטית לפופ מידטמפו קצבי משקף במדויק את מהלך השיר: תנועה מהתבוננות פנימית ושברירית אל קבלה אופטימית וחיונית. הבית</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,126 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון בוסקילה - מעליות</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שיר אמלי - חיכיתי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409459&amp;sid=596eb7a14186c6371d4797ff4f464372</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שיר אמלי - חיכיתי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שון בלו - אני בלו</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409458&amp;sid=596eb7a14186c6371d4797ff4f464372</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שון בלו - אני בלו</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>יסמין מועלם ומוש בן ארי – דרך</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C5" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%a1%d7%9e%d7%99%d7%9f-%d7%9e%d7%95%d7%a2%d7%9c%d7%9d-%d7%95%d7%9e%d7%95%d7%a9-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%93%d7%a8%d7%9a/</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v>השיר "דרך" של מוש בן ארי הוא אחד משירי המסע האינטימיים והחשופים ביותר ברפרטואר שלו – מסע שאינו רק גיאוגרפי, אלא בראש ובראשונה רגשי. על רקע הביצוע החי המשותף עם יסמין מועלם באמפי שוני, מקבל השיר שכבה נוספת של עומק,</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>יסמין מועלם ומוש בן ארי – דרך</v>
+        <v>אניה בוקשטיין – רק עכשיו</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אניה בוקשטיין – רק עכשיו</v>
+        <v>מועדון הקצב של אביהו פנחסוב – לא מפחד לרקוד</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a0%d7%99%d7%94-%d7%91%d7%95%d7%a7%d7%a9%d7%98%d7%99%d7%99%d7%9f-%d7%a8%d7%a7-%d7%a2%d7%9b%d7%a9%d7%99%d7%95/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%95%d7%a2%d7%93%d7%95%d7%9f-%d7%94%d7%a7%d7%a6%d7%91-%d7%a9%d7%9c-%d7%90%d7%91%d7%99%d7%94%d7%95-%d7%a4%d7%a0%d7%97%d7%a1%d7%95%d7%91-%d7%9c%d7%90-%d7%9e%d7%a4%d7%97%d7%93-%d7%9c%d7%a8%d7%a7/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-03</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אניה בוקשטיין שרה וידוי אישי עטוף בפופ קליט ומאיר, כזה שמצליח להיות גם קליל ומרקיד וגם חשוף ובוגר. המעבר המוזיקלי מסמבה שקטה ואקוסטית לפופ מידטמפו קצבי משקף במדויק את מהלך השיר: תנועה מהתבוננות פנימית ושברירית אל קבלה אופטימית וחיונית. הבית</v>
+        <v>איך להגדיר את המוסיקה? פאנק־סול ים־תיכוני עם הילולה בלקנית והפניית פנים לקהל? ואללה. נלך על זה. יש למישהו הגדרה אחרת למוסיקה של אביהו פנחסוב ומועדון הקצב שלו. מילים? כבר בשם השיר נמצא המפתח: זה קצב שמזמין תנועה וריקוד. המשפט החוזר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אניה בוקשטיין – רק עכשיו</v>
+        <v>מועדון הקצב של אביהו פנחסוב – לא מפחד לרקוד</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מועדון הקצב של אביהו פנחסוב – לא מפחד לרקוד</v>
+        <v>המשקפיים של נויפלד עם לאה שבת – על אמת</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%95%d7%a2%d7%93%d7%95%d7%9f-%d7%94%d7%a7%d7%a6%d7%91-%d7%a9%d7%9c-%d7%90%d7%91%d7%99%d7%94%d7%95-%d7%a4%d7%a0%d7%97%d7%a1%d7%95%d7%91-%d7%9c%d7%90-%d7%9e%d7%a4%d7%97%d7%93-%d7%9c%d7%a8%d7%a7/</v>
+        <v>https://yosmusic.com/%d7%94%d7%9e%d7%a9%d7%a7%d7%a4%d7%99%d7%99%d7%9d-%d7%a9%d7%9c-%d7%a0%d7%95%d7%99%d7%a4%d7%9c%d7%93-%d7%a2%d7%9d-%d7%9c%d7%90%d7%94-%d7%a9%d7%91%d7%aa-%d7%a2%d7%9c-%d7%90%d7%9e%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>איך להגדיר את המוסיקה? פאנק־סול ים־תיכוני עם הילולה בלקנית והפניית פנים לקהל? ואללה. נלך על זה. יש למישהו הגדרה אחרת למוסיקה של אביהו פנחסוב ומועדון הקצב שלו. מילים? כבר בשם השיר נמצא המפתח: זה קצב שמזמין תנועה וריקוד. המשפט החוזר</v>
+        <v>על אמת“ של לאה שבת עם "המשקפיים של נויפלד“ הוא דוגמה מובהקת ליצירה שמחברת בין פשטות ישירה לבין עומק רגשי, בין עייפות קיומית לבין תקווה עיקשת. השיר נפתח בהצהרה חשופה: – "אני קצת עייפה / מימים עצובים ולילות בלי שינה“.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מועדון הקצב של אביהו פנחסוב – לא מפחד לרקוד</v>
+        <v>המשקפיים של נויפלד עם לאה שבת – על אמת</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>המשקפיים של נויפלד עם לאה שבת – על אמת</v>
+        <v>שירי מימון – חמצן</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%9e%d7%a9%d7%a7%d7%a4%d7%99%d7%99%d7%9d-%d7%a9%d7%9c-%d7%a0%d7%95%d7%99%d7%a4%d7%9c%d7%93-%d7%a2%d7%9d-%d7%9c%d7%90%d7%94-%d7%a9%d7%91%d7%aa-%d7%a2%d7%9c-%d7%90%d7%9e%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%99%d7%a8%d7%99-%d7%9e%d7%99%d7%9e%d7%95%d7%9f-%d7%97%d7%9e%d7%a6%d7%9f/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-04</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>על אמת“ של לאה שבת עם "המשקפיים של נויפלד“ הוא דוגמה מובהקת ליצירה שמחברת בין פשטות ישירה לבין עומק רגשי, בין עייפות קיומית לבין תקווה עיקשת. השיר נפתח בהצהרה חשופה: – "אני קצת עייפה / מימים עצובים ולילות בלי שינה“.</v>
+        <v>"חמצן“ פועל במרחב שבין בלדה אישית לבין הצהרה דורית, ובכך מצליח להיות גם אינטימי מאוד וגם רחב-היקף. שירי מימון אינה מתייחסת לאירוע ספציפי, אלא מצב מתמשך: "את לא מבינה למה אין לך אוויר“, "הראש כבד וקצת קשה לנשום“. אלה תיאורים</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>המשקפיים של נויפלד עם לאה שבת – על אמת</v>
+        <v>שירי מימון – חמצן</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שירי מימון – חמצן</v>
+        <v>בן אל תבורי - מי אני</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%99%d7%a8%d7%99-%d7%9e%d7%99%d7%9e%d7%95%d7%9f-%d7%97%d7%9e%d7%a6%d7%9f/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409479&amp;sid=f25a1cf68326f713b4334e0bd420caa5</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-04</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"חמצן“ פועל במרחב שבין בלדה אישית לבין הצהרה דורית, ובכך מצליח להיות גם אינטימי מאוד וגם רחב-היקף. שירי מימון אינה מתייחסת לאירוע ספציפי, אלא מצב מתמשך: "את לא מבינה למה אין לך אוויר“, "הראש כבד וקצת קשה לנשום“. אלה תיאורים</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,126 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שירי מימון – חמצן</v>
+        <v>בן אל תבורי - מי אני</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אמיר ישראל - פוצי מוצי</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409478&amp;sid=f25a1cf68326f713b4334e0bd420caa5</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אמיר ישראל - פוצי מוצי</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>אופק יפרח אזולאי - מה לי ולרומנטיקה</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409477&amp;sid=f25a1cf68326f713b4334e0bd420caa5</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>אופק יפרח אזולאי - מה לי ולרומנטיקה</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>עדן חסון – חוזר לעצמי</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C5" t="str">
+        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%97%d7%a1%d7%95%d7%9f-%d7%97%d7%95%d7%96%d7%a8-%d7%9c%d7%a2%d7%a6%d7%9e%d7%99/</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>השיר ממשיך ומעמיק את הקו האישי־ווידויי מה שנפתח באופן מובהק ב־"אדם שבור“ –  כתיבה על שבר פנימי שקט, לא דרמטי-מתפרץ אלא יומיומי, מצטבר, אנושי מאוד. הבית הראשון מציג רשימת פעולות פשוטות: "עוד סיגריה במרפסת, שבע קפה שחור“, "מים חמים על</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>עדן חסון – חוזר לעצמי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בן אל תבורי - מי אני</v>
+        <v>משה פרץ - ימים טובים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409479&amp;sid=f25a1cf68326f713b4334e0bd420caa5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409483&amp;sid=66852f0d514e2c5d13155a5d5d0f0788</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-04</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בן אל תבורי - מי אני</v>
+        <v>משה פרץ - ימים טובים</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אמיר ישראל - פוצי מוצי</v>
+        <v>חיים ציפל - תדליק לי נר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409478&amp;sid=f25a1cf68326f713b4334e0bd420caa5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409482&amp;sid=66852f0d514e2c5d13155a5d5d0f0788</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-04</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אמיר ישראל - פוצי מוצי</v>
+        <v>חיים ציפל - תדליק לי נר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אופק יפרח אזולאי - מה לי ולרומנטיקה</v>
+        <v>המשקפיים של נויפלד עם לאה שבת - על אמת</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409477&amp;sid=f25a1cf68326f713b4334e0bd420caa5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409481&amp;sid=66852f0d514e2c5d13155a5d5d0f0788</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-04</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אופק יפרח אזולאי - מה לי ולרומנטיקה</v>
+        <v>המשקפיים של נויפלד עם לאה שבת - על אמת</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עדן חסון – חוזר לעצמי</v>
+        <v>דניאל כהן - למה פתאום חזרת</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C5" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%97%d7%a1%d7%95%d7%9f-%d7%97%d7%95%d7%96%d7%a8-%d7%9c%d7%a2%d7%a6%d7%9e%d7%99/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409480&amp;sid=66852f0d514e2c5d13155a5d5d0f0788</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-04</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>השיר ממשיך ומעמיק את הקו האישי־ווידויי מה שנפתח באופן מובהק ב־"אדם שבור“ –  כתיבה על שבר פנימי שקט, לא דרמטי-מתפרץ אלא יומיומי, מצטבר, אנושי מאוד. הבית הראשון מציג רשימת פעולות פשוטות: "עוד סיגריה במרפסת, שבע קפה שחור“, "מים חמים על</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -583,7 +583,7 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עדן חסון – חוזר לעצמי</v>
+        <v>דניאל כהן - למה פתאום חזרת</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>משה פרץ - ימים טובים</v>
+        <v>אופק יפרח אזולאי - מה לי ולרומנטיקה קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409483&amp;sid=66852f0d514e2c5d13155a5d5d0f0788</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409477&amp;sid=81f569bfbe129aebcaf4b317ba1f5acf</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-04</v>
@@ -469,126 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>משה פרץ - ימים טובים</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>חיים ציפל - תדליק לי נר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409482&amp;sid=66852f0d514e2c5d13155a5d5d0f0788</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>חיים ציפל - תדליק לי נר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>המשקפיים של נויפלד עם לאה שבת - על אמת</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409481&amp;sid=66852f0d514e2c5d13155a5d5d0f0788</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>המשקפיים של נויפלד עם לאה שבת - על אמת</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>דניאל כהן - למה פתאום חזרת</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409480&amp;sid=66852f0d514e2c5d13155a5d5d0f0788</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>דניאל כהן - למה פתאום חזרת</v>
+        <v>אופק יפרח אזולאי - מה לי ולרומנטיקה קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אופק יפרח אזולאי - מה לי ולרומנטיקה קאבר</v>
+        <v>נדב חנציס - אהבה ראשונה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409477&amp;sid=81f569bfbe129aebcaf4b317ba1f5acf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409484&amp;sid=85c2be9d7b769a967dd94f06e90e8ff2</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-04</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אופק יפרח אזולאי - מה לי ולרומנטיקה קאבר</v>
+        <v>נדב חנציס - אהבה ראשונה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נדב חנציס - אהבה ראשונה</v>
+        <v>תמר כהנא - את הים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409484&amp;sid=85c2be9d7b769a967dd94f06e90e8ff2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409493&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-04</v>
@@ -469,12 +469,278 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נדב חנציס - אהבה ראשונה</v>
+        <v>תמר כהנא - את הים</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>תמר אופיר - שיר טיפול</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409491&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>תמר אופיר - שיר טיפול</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>שירי מימון - חמצן</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409490&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>שירי מימון - חמצן</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>שילה אליה - אם הייתי יכול</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409489&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>שילה אליה - אם הייתי יכול</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>שי שמואל פחימה - החיים</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409488&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>שי שמואל פחימה - החיים</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>סטפן לגר - הלוך חזור</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409487&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>סטפן לגר - הלוך חזור</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>נתי - תמיתי לי בלילה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409486&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>נתי - תמיתי לי בלילה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>נדב חנציס - מפחד להתגבר עלייך</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409485&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>נדב חנציס - מפחד להתגבר עלייך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמר כהנא - את הים</v>
+        <v>עדן חסון - חוזר לעצמי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409493&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409494&amp;sid=7f8aa5df0b2c0a2c1ebe6d5b5062b03c</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-04</v>
@@ -469,278 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמר כהנא - את הים</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>תמר אופיר - שיר טיפול</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409491&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>תמר אופיר - שיר טיפול</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שירי מימון - חמצן</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409490&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שירי מימון - חמצן</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>שילה אליה - אם הייתי יכול</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409489&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>שילה אליה - אם הייתי יכול</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>שי שמואל פחימה - החיים</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409488&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>שי שמואל פחימה - החיים</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>סטפן לגר - הלוך חזור</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409487&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>סטפן לגר - הלוך חזור</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>נתי - תמיתי לי בלילה</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409486&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>נתי - תמיתי לי בלילה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>נדב חנציס - מפחד להתגבר עלייך</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409485&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>נדב חנציס - מפחד להתגבר עלייך</v>
+        <v>עדן חסון - חוזר לעצמי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עדן חסון - חוזר לעצמי</v>
+        <v>משה פרץ – ימים טובים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409494&amp;sid=7f8aa5df0b2c0a2c1ebe6d5b5062b03c</v>
+        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%94-%d7%a4%d7%a8%d7%a5-%d7%99%d7%9e%d7%99%d7%9d-%d7%98%d7%95%d7%91%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>"ימים טובים" של משה פרץ משתייך לקו המוכר שלו: פופ-מיינסטרים מלודי, רגשי, נגיש מאוד, עם שילוב בין כאב אישי לבין נחמה פשוטה ואופטימית. לב השיר עוסק ברעיון פשוט: המתנות הגדולות של החיים אינן בהכרח אירועים דרמטיים, אלא רגעים קטנים –</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עדן חסון - חוזר לעצמי</v>
+        <v>משה פרץ – ימים טובים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>משה פרץ – ימים טובים</v>
+        <v>רמי מור - הלב שלך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-05</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%94-%d7%a4%d7%a8%d7%a5-%d7%99%d7%9e%d7%99%d7%9d-%d7%98%d7%95%d7%91%d7%99%d7%9d/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409510&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-05</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"ימים טובים" של משה פרץ משתייך לקו המוכר שלו: פופ-מיינסטרים מלודי, רגשי, נגיש מאוד, עם שילוב בין כאב אישי לבין נחמה פשוטה ואופטימית. לב השיר עוסק ברעיון פשוט: המתנות הגדולות של החיים אינן בהכרח אירועים דרמטיים, אלא רגעים קטנים –</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,582 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>משה פרץ – ימים טובים</v>
+        <v>רמי מור - הלב שלך</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>קורין גמליאל - 2 בלילה</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409509&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>קורין גמליאל - 2 בלילה</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>קארין אבלמן - מה לא ניצחנו</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409508&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>קארין אבלמן - מה לא ניצחנו</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מרדכי בן ראובן - שמה הדסה</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409507&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מרדכי בן ראובן - שמה הדסה</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מאי ספדיה - יותר מכולן</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409506&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מאי ספדיה - יותר מכולן</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ליאור פינטו - תכף חורף</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409505&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>ליאור פינטו - תכף חורף</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>טל ורסנו - נופל מגעגוע</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409504&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>טל ורסנו - נופל מגעגוע</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>טונה - הייתי שם</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409503&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>טונה - הייתי שם</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>זהר מנור - אל תדאג</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409502&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>זהר מנור - אל תדאג</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>היוצרים - משתכרת מתירוש</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409501&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>היוצרים - משתכרת מתירוש</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>‎גלעד יחיא - חיבוק אחד קטן</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409500&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>‎גלעד יחיא - חיבוק אחד קטן</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אריאל אזולאי - היא שולטת בי</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409499&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אריאל אזולאי - היא שולטת בי</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>איתי לוי - בשעות הבודדות</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409498&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>איתי לוי - בשעות הבודדות</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אופיר חיים - צא אל החלום</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409497&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אופיר חיים - צא אל החלום</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אדיר ניזרי - בטוב וגם ברע בית"ר</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409496&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אדיר ניזרי - בטוב וגם ברע בית"ר</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>אדיר יהודה - ריבונו של עולם</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409495&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>אדיר יהודה - ריבונו של עולם</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שחר סאול - שני פושעים</v>
+        <v>איתי לוי – בשעות הבודדות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409512&amp;sid=515df5a47af0a221d79f45b61123b49c</v>
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%aa%d7%99-%d7%9c%d7%95%d7%99-%d7%91%d7%a9%d7%a2%d7%95%d7%aa-%d7%94%d7%91%d7%95%d7%93%d7%93%d7%95%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "בשעות הבודדות" של איתי לוי ממקם את עצמו בבירור בתוך אחד הנתיבים השחוקים ביותר של הז’אנר הים־תיכוני הישראלי: הגבר הפגוע, המובס, המתקרבן – מול אישה שעזבה, שותקת, ואחראית לכאבו. הנרטיב מוכר עד לעייפה: היא נטשה, הוא נשאר לבד, סובל,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שחר סאול - שני פושעים</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שחר סאול - מאחל לך טוב</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-05</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409511&amp;sid=515df5a47af0a221d79f45b61123b49c</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-05</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שחר סאול - מאחל לך טוב</v>
+        <v>איתי לוי – בשעות הבודדות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>איתי לוי – בשעות הבודדות</v>
+        <v>שמעון בוסקילה – מעליות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-06</v>
+        <v>2026-02-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%aa%d7%99-%d7%9c%d7%95%d7%99-%d7%91%d7%a9%d7%a2%d7%95%d7%aa-%d7%94%d7%91%d7%95%d7%93%d7%93%d7%95%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9e%d7%a2%d7%95%d7%9f-%d7%91%d7%95%d7%a1%d7%a7%d7%99%d7%9c%d7%94-%d7%9e%d7%a2%d7%9c%d7%99%d7%95%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-06</v>
+        <v>2026-02-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "בשעות הבודדות" של איתי לוי ממקם את עצמו בבירור בתוך אחד הנתיבים השחוקים ביותר של הז’אנר הים־תיכוני הישראלי: הגבר הפגוע, המובס, המתקרבן – מול אישה שעזבה, שותקת, ואחראית לכאבו. הנרטיב מוכר עד לעייפה: היא נטשה, הוא נשאר לבד, סובל,</v>
+        <v>שמעון בוסקילה  שר מצב של בין געגוע חזק לבין ניסיון להתאפס. “רק התאפסתי לא התרגלתי” – חוסר יציבות רגשית, “שורף מגעגועים” – געגוע פיזי, כמעט כואב, “לטפס על הקירות” – חוסר שקט, עצבים, בדידות זה אדם שמתפקד ביום-יום (קם, שוטף</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>איתי לוי – בשעות הבודדות</v>
+        <v>שמעון בוסקילה – מעליות</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון בוסקילה – מעליות</v>
+        <v>הפטריקים הפרויקט של דודי לוי ואבטיפוס – מלאך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9e%d7%a2%d7%95%d7%9f-%d7%91%d7%95%d7%a1%d7%a7%d7%99%d7%9c%d7%94-%d7%9e%d7%a2%d7%9c%d7%99%d7%95%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%98%d7%a8%d7%99%d7%a7%d7%99%d7%9d-%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%93%d7%95%d7%93%d7%99-%d7%9c%d7%95%d7%99-%d7%95%d7%90%d7%91%d7%98%d7%99%d7%a4%d7%95%d7%a1-2/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-07</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>שמעון בוסקילה  שר מצב של בין געגוע חזק לבין ניסיון להתאפס. “רק התאפסתי לא התרגלתי” – חוסר יציבות רגשית, “שורף מגעגועים” – געגוע פיזי, כמעט כואב, “לטפס על הקירות” – חוסר שקט, עצבים, בדידות זה אדם שמתפקד ביום-יום (קם, שוטף</v>
+        <v>"מלאך” של דודי לוי הוא טקסט לירי שמרחף בין אגדה לחלום שבור, ובביצוע המחודש עם הפטריקים, ההרמוניה מבליטה את מה שתמיד היה בו: יופי שקט עם סדק עמוק בפנים. המלאך מתואר כיצור חופשי, אבל החופש הזה מוגבל: "מלאך נוגה מביט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון בוסקילה – מעליות</v>
+        <v>הפטריקים הפרויקט של דודי לוי ואבטיפוס – מלאך</v>
       </c>
     </row>
   </sheetData>
